--- a/salida/transporte_diario.xlsx
+++ b/salida/transporte_diario.xlsx
@@ -4213,7 +4213,7 @@
         <v>119.6</v>
       </c>
       <c r="J25" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
